--- a/doc/routes/schéma_route.xlsx
+++ b/doc/routes/schéma_route.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaysb\Documents\GitHub\p_web_265_books\doc\routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63B62E23-324F-435E-917F-876DF89A875D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{236D3AC5-C5C0-4F2A-A98A-FC4B9CD85BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7993F311-0621-4DD8-9E87-7C37D4C61821}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -188,12 +189,18 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -288,7 +295,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -299,8 +306,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -635,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6E998F5-60FC-4790-B9FD-DED293EBCCD9}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="27.59765625" bestFit="1" customWidth="1"/>
@@ -644,7 +653,7 @@
     <col min="4" max="4" width="34.53125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -653,24 +662,25 @@
       <c r="D1" s="8"/>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="14.65" thickBot="1">
+      <c r="F2" s="11"/>
+    </row>
+    <row r="3" spans="1:6" ht="14.65" thickBot="1">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -687,8 +697,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.65" thickBot="1"/>
-    <row r="5" spans="1:5">
+    <row r="4" spans="1:6" ht="14.65" thickBot="1"/>
+    <row r="5" spans="1:6">
       <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
@@ -697,7 +707,7 @@
       <c r="D5" s="8"/>
       <c r="E5" s="9"/>
     </row>
-    <row r="6" spans="1:5" ht="14.65" thickBot="1">
+    <row r="6" spans="1:6" ht="14.65" thickBot="1">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -714,8 +724,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.65" thickBot="1"/>
-    <row r="8" spans="1:5">
+    <row r="7" spans="1:6" ht="14.65" thickBot="1"/>
+    <row r="8" spans="1:6">
       <c r="A8" s="7" t="s">
         <v>10</v>
       </c>
@@ -724,24 +734,24 @@
       <c r="D8" s="8"/>
       <c r="E8" s="9"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.65" thickBot="1">
+    <row r="10" spans="1:6" ht="14.65" thickBot="1">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -758,8 +768,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="14.65" thickBot="1"/>
-    <row r="12" spans="1:5">
+    <row r="11" spans="1:6" ht="14.65" thickBot="1"/>
+    <row r="12" spans="1:6">
       <c r="A12" s="7" t="s">
         <v>18</v>
       </c>
@@ -768,24 +778,24 @@
       <c r="D12" s="8"/>
       <c r="E12" s="9"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.65" thickBot="1">
+    <row r="14" spans="1:6" ht="14.65" thickBot="1">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
@@ -800,7 +810,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="14.65" thickBot="1"/>
+    <row r="16" spans="1:6" ht="14.65" thickBot="1"/>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
         <v>24</v>
@@ -814,13 +824,13 @@
       <c r="A18" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" t="s">
         <v>21</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -831,13 +841,12 @@
       <c r="A19" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C19" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="10"/>
       <c r="E19" s="2" t="s">
         <v>27</v>
       </c>
@@ -846,7 +855,7 @@
       <c r="A20" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="13" t="s">
         <v>25</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -871,16 +880,13 @@
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5" ht="14.65" thickBot="1">
       <c r="A24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="13" t="s">
         <v>2</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -905,13 +911,13 @@
       <c r="A27" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="2" t="s">
@@ -922,13 +928,13 @@
       <c r="A28" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" t="s">
         <v>30</v>
       </c>
       <c r="E28" s="2" t="s">
@@ -939,13 +945,13 @@
       <c r="A29" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" t="s">
         <v>29</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" t="s">
         <v>30</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -956,13 +962,13 @@
       <c r="A30" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" t="s">
         <v>29</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" t="s">
         <v>30</v>
       </c>
       <c r="E30" s="2" t="s">
@@ -973,13 +979,13 @@
       <c r="A31" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" t="s">
         <v>30</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -990,13 +996,13 @@
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" t="s">
         <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
